--- a/module-wise-test-scenarios-and-cases.xlsx
+++ b/module-wise-test-scenarios-and-cases.xlsx
@@ -528,7 +528,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>M1 Top Navigation Bar</t>
+          <t>M1 Top Navigation</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -546,7 +546,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup Page</t>
+          <t>M2 Sign Up</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -564,7 +564,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>M3 Login Page</t>
+          <t>M3 Login</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>M4 Logout Action</t>
+          <t>M4 Logout</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>M7 New Post</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -677,10 +677,10 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -706,17 +706,17 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="75" customWidth="1" min="10" max="10"/>
-    <col width="75" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>M1 Top Navigation Bar</t>
+          <t>M1 Top Navigation</t>
         </is>
       </c>
     </row>
@@ -762,17 +762,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>M1 Top Nav</t>
+          <t>Top Navigation</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Anonymous nav shows Login + Sign up</t>
+          <t>Visitor sees public navigation options</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Verify the nav renders Login and Sign up when no session is active.</t>
+          <t>Verify that visitors who are not logged in see Login and Sign Up options.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>M1 Top Nav</t>
+          <t>Top Navigation</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Logged-in nav shows New Post + greeting + Logout</t>
+          <t>Logged-in user sees author navigation</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Verify auth-aware links and HTML-escaped greeting.</t>
+          <t>Verify that logged-in users see New Post, a personal greeting, and Logout.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>M1 Top Nav</t>
+          <t>Top Navigation</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Brand link returns user to the homepage</t>
+          <t>User can return to the home page from any page</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Confirm clicking 'MiniBlog' navigates to /.</t>
+          <t>Verify that clicking the MiniBlog logo always opens the home page.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>M1 Top Nav</t>
+          <t>Top Navigation</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Anonymous nav shows Login + Sign up</t>
+          <t>Visitor sees Login and Sign Up options in the top menu</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -937,23 +937,23 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Browser has no auth in localStorage.</t>
+          <t>The user is not logged in.</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>1. Open http://localhost:8080/.
-2. Inspect the #nav-links container.</t>
+          <t>1. Open the MiniBlog home page.
+2. Look at the top navigation menu.</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Login and Sign up links visible. New Post / greeting / Logout are NOT visible.</t>
+          <t>The top menu clearly shows Login and Sign up options. New Post, the greeting, and Logout are not visible.</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>M1 Top Nav</t>
+          <t>Top Navigation</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Logged-in nav shows New Post + greeting + Logout</t>
+          <t>Logged-in user sees New Post, greeting, and Logout in the top menu</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>User signed up/logged in.</t>
+          <t>The user has a valid account.</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>username = ali_khan_2026</t>
+          <t>Username: ali.khan</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1. Log in as ali_khan_2026.
-2. Land on /.
-3. Read #nav-links container.</t>
+          <t>1. Log in as Ali Khan.
+2. Open the home page.
+3. Look at the top navigation menu.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>New Post link, 'Hi, ali_khan_2026' greeting, and Logout button visible. Login/Sign up NOT visible.</t>
+          <t>The top menu shows New Post, a greeting reading "Hi, ali.khan", and a Logout button. Login and Sign up are no longer shown.</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>M1 Top Nav</t>
+          <t>Top Navigation</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Greeting HTML-escapes username with special chars</t>
+          <t>Username with special characters is shown safely in the greeting</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1054,23 +1054,23 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>User created via API (UI minlength applies otherwise).</t>
+          <t>An account exists whose username contains special characters.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>username = &lt;b&gt;boldUser&lt;/b&gt; (sample realistic invalid display)</t>
+          <t>Username: Ali &lt;Khan&gt;</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>1. Sign up the user via API to bypass UI cap if needed.
-2. Log in and load homepage.</t>
+          <t>1. Log in with the special-character username.
+2. Look at the greeting in the top menu.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Greeting renders the literal text 'Hi, &lt;b&gt;boldUser&lt;/b&gt;'; no &lt;b&gt; tag is rendered (XSS-safe).</t>
+          <t>The greeting displays the special characters as plain readable text. The page does not break and no unintended formatting appears.</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>M1 Top Nav</t>
+          <t>Top Navigation</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Brand link from /create.html returns to /</t>
+          <t>User returns to the home page from the New Post page using the logo</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1112,23 +1112,23 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Logged in.</t>
+          <t>The user is logged in.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1. Open /create.html.
-2. Click the 'MiniBlog' brand link.</t>
+          <t>1. Open the New Post page.
+2. Click the MiniBlog logo in the top menu.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>URL becomes /. 'Latest posts' heading is visible.</t>
+          <t>The home page is displayed with the "Latest posts" heading.</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>M1 Top Nav</t>
+          <t>Top Navigation</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Brand link from /post.html returns to /</t>
+          <t>User returns to the home page from a post detail page using the logo</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1170,23 +1170,23 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Any post exists.</t>
+          <t>At least one post exists.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>/post.html?id=1</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html?id=1.
-2. Click brand link.</t>
+          <t>1. Open any post's detail page.
+2. Click the MiniBlog logo.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>URL becomes /. Posts list visible.</t>
+          <t>The home page is displayed with the list of posts.</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>M1 Top Nav</t>
+          <t>Top Navigation</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Logout button only rendered for logged-in users</t>
+          <t>Logout button is hidden when the user is not logged in</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1228,23 +1228,23 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Anonymous.</t>
+          <t>The user is not logged in.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1. Visit /, /signup.html, /login.html.
-2. Inspect for #logout-btn.</t>
+          <t>1. While not logged in, open the home page, the Sign Up page, and the Login page in turn.
+2. Look for a Logout button on each.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>#logout-btn is not present on any page while anonymous.</t>
+          <t>No Logout button is shown on any of the three pages.</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="75" customWidth="1" min="10" max="10"/>
-    <col width="75" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>M2 Signup Page</t>
+          <t>M2 Sign Up</t>
         </is>
       </c>
     </row>
@@ -1329,17 +1329,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Successful signup with valid data</t>
+          <t>New visitor can register an account successfully</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Verify happy-path signup with auto-login and redirect to /.</t>
+          <t>Verify that a visitor can register with valid details and is automatically logged in.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1356,17 +1356,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Required-field validation</t>
+          <t>Sign Up form enforces required fields</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Verify client (HTML5) + server required errors.</t>
+          <t>Verify that empty required fields are not accepted.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1383,17 +1383,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Password length boundary</t>
+          <t>Password length must be at least six characters</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Verify min-6 boundary at client and server.</t>
+          <t>Verify the minimum password length rule.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Duplicate username/email blocked</t>
+          <t>Duplicate username or email is not allowed</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Verify uniqueness constraint enforcement.</t>
+          <t>Verify uniqueness of username and email at registration.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Logged-in user auto-redirected from /signup.html</t>
+          <t>Logged-in user is redirected away from the Sign Up page</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Verify guard prevents signup form for active session.</t>
+          <t>Verify that already logged-in users do not see the Sign Up form.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Sign up with realistic valid data</t>
+          <t>User registers a new account with valid details</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1558,24 +1558,26 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>User does not exist.</t>
+          <t>The user does not have an existing account.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>username: ali_khan_2026; email: ali.khan@gmail.com; password: Passw0rd!</t>
+          <t>Username: ali.khan
+Email: ali.khan@gmail.com
+Password: Passw0rd!</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html.
-2. Fill all three fields.
-3. Click 'Sign up'.</t>
+          <t>1. Open the Sign Up page.
+2. Enter the username, email, and password.
+3. Click Sign up.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>URL redirects to /. Nav switches to logged-in state with greeting 'Hi, ali_khan_2026'. localStorage token + user populated.</t>
+          <t>The account is created and the user is taken to the home page, automatically logged in. The greeting "Hi, ali.khan" appears in the top menu.</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1594,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Submit empty form blocked by HTML5</t>
+          <t>Sign Up form blocks submission when no fields are filled</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1617,23 +1619,23 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Browser anonymous.</t>
+          <t>The user is on the Sign Up page.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>All fields empty.</t>
+          <t>Leave Username, Email, and Password blank.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html.
-2. Click 'Sign up' without filling.</t>
+          <t>1. Open the Sign Up page.
+2. Click Sign up without entering any details.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Browser shows native required-field tooltip on first empty input. No network request fires.</t>
+          <t>The form does not submit. The first empty required field shows a "please fill out this field" prompt.</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1652,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Server-side required-fields error (bypass HTML5)</t>
+          <t>Relevant validation message is shown when required fields are missing</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1675,22 +1677,24 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>API directly hit.</t>
+          <t>The user is registering without filling all required fields.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>POST {} to /api/auth/signup.</t>
+          <t>Username: blank
+Email: blank
+Password: blank</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>1. Send POST /api/auth/signup with empty body.</t>
+          <t>1. Submit a registration request with all fields empty.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>HTTP 400 with body { error: 'username, email and password are required' }.</t>
+          <t>The validation message "username, email and password are required" is displayed and the account is not created.</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1711,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Password exactly 6 chars accepted</t>
+          <t>Password with exactly six characters is accepted</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1732,24 +1736,26 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>User does not exist.</t>
+          <t>The user does not have an existing account.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>username: fatima_a; email: fatima.a@gmail.com; password: abc123 (6 chars)</t>
+          <t>Username: fatima.a
+Email: fatima.a@gmail.com
+Password: abc123</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html.
-2. Fill fields with data above.
-3. Submit.</t>
+          <t>1. Open the Sign Up page.
+2. Enter the data above.
+3. Click Sign up.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Account created; redirected to /. Logged-in nav shows greeting 'Hi, fatima_a'.</t>
+          <t>The account is created and the user is taken to the home page. The greeting "Hi, fatima.a" appears in the top menu.</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1772,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Password 5 chars rejected (server validation)</t>
+          <t>Password shorter than six characters is rejected</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1791,24 +1797,26 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Browser anonymous.</t>
+          <t>The user is on the Sign Up page.</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>password = abc12 (5 chars)</t>
+          <t>Username: fatima.a
+Email: fatima.a@gmail.com
+Password: Ali@1</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html.
-2. Force-set password value to 'abc12' (bypass HTML5).
-3. Submit.</t>
+          <t>1. Open the Sign Up page.
+2. Enter the data above.
+3. Click Sign up.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Inline error banner: 'Password must be at least 6 characters' (HTTP 400).</t>
+          <t>The validation message "Password must be at least 6 characters" is displayed and the account is not created.</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1833,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Username minlength HTML5 enforced (2 chars)</t>
+          <t>Username shorter than three characters is not accepted</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1850,23 +1858,26 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Browser anonymous.</t>
+          <t>The user is on the Sign Up page.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>username = ab</t>
+          <t>Username: ab
+Email: bilal@gmail.com
+Password: Passw0rd!</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html.
-2. Type 'ab' in username, fill remaining fields, submit.</t>
+          <t>1. Open the Sign Up page.
+2. Enter the data above.
+3. Click Sign up.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Browser shows native validation tooltip on username; form not submitted.</t>
+          <t>The form does not submit. The Username field shows a prompt asking for at least three characters.</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1894,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Username maxlength HTML5 enforced (&gt;30 chars)</t>
+          <t>Username field stops accepting input after thirty characters</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1908,22 +1919,23 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Browser anonymous.</t>
+          <t>The user is on the Sign Up page.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>username = 31 chars 'a'</t>
+          <t>Type a 31-letter username (e.g., "a" repeated 31 times).</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>1. Type 31 'a' chars into username field.</t>
+          <t>1. Open the Sign Up page.
+2. Type 31 letters into the Username field.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Field accepts only first 30 chars (HTML5 maxlength behavior).</t>
+          <t>Only the first thirty letters are accepted in the Username field.</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1952,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Duplicate email blocked</t>
+          <t>Sign up is rejected when the email is already registered</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1965,23 +1977,26 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>ali.khan@gmail.com already exists.</t>
+          <t>An account with the email ali.khan@gmail.com already exists.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>username: ali_2; email: ali.khan@gmail.com; password: Passw0rd!</t>
+          <t>Username: ali.khan2
+Email: ali.khan@gmail.com
+Password: Passw0rd!</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html.
-2. Submit with duplicate email.</t>
+          <t>1. Open the Sign Up page.
+2. Enter the data above.
+3. Click Sign up.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Error banner: 'Username or email already in use' (HTTP 409). User stays on /signup.html.</t>
+          <t>The validation message "Username or email already in use" is displayed and the user remains on the Sign Up page.</t>
         </is>
       </c>
     </row>
@@ -1998,12 +2013,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Duplicate username blocked</t>
+          <t>Sign up is rejected when the username is already registered</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2023,23 +2038,26 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>ali_khan_2026 already exists.</t>
+          <t>A user named ali.khan already exists.</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>username: ali_khan_2026; email: new.email@gmail.com; password: Passw0rd!</t>
+          <t>Username: ali.khan
+Email: new.email@gmail.com
+Password: Passw0rd!</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html.
-2. Submit with duplicate username.</t>
+          <t>1. Open the Sign Up page.
+2. Enter the data above.
+3. Click Sign up.</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Error banner: 'Username or email already in use' (HTTP 409).</t>
+          <t>The validation message "Username or email already in use" is displayed.</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2074,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Trims leading/trailing whitespace on username + email</t>
+          <t>Username and email are saved without leading or trailing spaces</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2081,23 +2099,26 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>User does not exist.</t>
+          <t>The user does not have an existing account.</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>username: '  bilal_dev  '; email: '  bilal@gmail.com  '; password: Passw0rd!</t>
+          <t>Username: "  bilal.dev  "
+Email: "  bilal@gmail.com  "
+Password: Passw0rd!</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html.
-2. Fill fields with padded values, submit.</t>
+          <t>1. Open the Sign Up page.
+2. Enter the username and email with extra spaces, and a valid password.
+3. Click Sign up.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Account created. Greeting reads 'Hi, bilal_dev' (trimmed) and stored email is bilal@gmail.com.</t>
+          <t>The account is created. The greeting reads "Hi, bilal.dev" without extra spaces.</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2135,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Email field rejects malformed address (HTML5)</t>
+          <t>Sign up does not accept an invalid email format</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2139,23 +2160,26 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Browser anonymous.</t>
+          <t>The user is on the Sign Up page.</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>email = not-an-email</t>
+          <t>Username: kashan
+Email: ali.khan.gmail.com
+Password: Passw0rd!</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html.
-2. Type 'not-an-email' in email, fill rest, submit.</t>
+          <t>1. Open the Sign Up page.
+2. Enter the data above.
+3. Click Sign up.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Browser shows native invalid-email tooltip; form not submitted.</t>
+          <t>The form does not submit. The Email field shows a "please enter a valid email address" prompt.</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2196,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Logged-in user auto-redirected from /signup.html</t>
+          <t>Logged-in user is redirected away from the Sign Up page</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2197,22 +2221,22 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>token + user already in localStorage.</t>
+          <t>The user is already logged in.</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html directly while logged in.</t>
+          <t>1. While logged in, open the Sign Up page directly.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Browser navigates to / immediately. Signup form is not rendered.</t>
+          <t>The user is taken straight to the home page. The Sign Up form is not shown.</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2253,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Successful signup persists session in localStorage</t>
+          <t>User remains logged in after refreshing the page</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2254,23 +2278,25 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>User does not exist.</t>
+          <t>The user does not have an existing account.</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>username: zara_t; email: zara.tariq@gmail.com; password: Strong#22</t>
+          <t>Username: zara.t
+Email: zara.tariq@gmail.com
+Password: Strong#22</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>1. Sign up with the data above.
-2. Read localStorage 'token' and 'user'.</t>
+          <t>1. Sign up using the data above.
+2. Refresh the home page.</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>token is a non-empty JWT string. user is JSON containing id, username='zara_t', email='zara.tariq@gmail.com'.</t>
+          <t>The user remains logged in. The greeting "Hi, zara.t" continues to be shown after refresh.</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2313,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>M2 Signup</t>
+          <t>Sign Up</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>'Already have an account? Log in' link works</t>
+          <t>"Already have an account? Log in" link opens the Login page</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2312,23 +2338,23 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Browser anonymous.</t>
+          <t>The user is on the Sign Up page.</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>1. Open /signup.html.
-2. Click 'Log in' link.</t>
+          <t>1. Open the Sign Up page.
+2. Click the Log in link at the bottom.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>URL becomes /login.html. 'Log in' heading visible.</t>
+          <t>The Login page is displayed with the "Log in" heading.</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2357,17 +2383,17 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="75" customWidth="1" min="10" max="10"/>
-    <col width="75" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>M3 Login Page</t>
+          <t>M3 Login</t>
         </is>
       </c>
     </row>
@@ -2413,17 +2439,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>M3 Login</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Successful login with valid credentials</t>
+          <t>Registered user can log in with valid credentials</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Verify happy-path login + session creation.</t>
+          <t>Verify the happy-path login flow.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2440,17 +2466,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>M3 Login</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Required-field validation</t>
+          <t>Login form enforces required fields</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Verify required errors at client + server.</t>
+          <t>Verify that empty fields are not accepted.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2467,17 +2493,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>M3 Login</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Invalid credentials handling</t>
+          <t>Invalid credentials are rejected with a clear message</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Verify generic auth-failure messaging.</t>
+          <t>Verify that wrong credentials show a generic invalid-credentials message.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -2494,17 +2520,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>M3 Login</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Logged-in user auto-redirected from /login.html</t>
+          <t>Logged-in user is redirected away from the Login page</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Verify guard prevents login form when authenticated.</t>
+          <t>Verify the guard for already-logged-in users.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2513,321 +2539,197 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Test Cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Scenario ID</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Module Name</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Coverage Type</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Remember me option appears and behaves correctly on the Login page</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Verify that the Remember me checkbox is shown on the Login page, is unchecked by default, and toggles when its label is clicked.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Positive, UI, Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-06</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Remember me extends the session across browser restarts</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Verify that ticking Remember me at login keeps the user signed in for thirty days, even after the browser is closed.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Positive, Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-07</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Without Remember me, the session ends with the current browser tab</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Verify that logging in without Remember me ends the session when the tab is closed and the token only lasts one day.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Positive, Boundary, Functional</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TC-LGN-01</t>
+          <t>TS-LGN-08</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>TS-LGN-01</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>M3 Login</t>
+          <t>Remember me does not bypass credential validation</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Log in with correct credentials</t>
+          <t>Verify that ticking Remember me does not allow login with wrong credentials.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Smoke</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>User ali.khan@gmail.com / Passw0rd! exists.</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>email: ali.khan@gmail.com; password: Passw0rd!</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>1. Open /login.html.
-2. Fill email + password.
-3. Click 'Log in'.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>URL redirects to /. Nav shows greeting 'Hi, ali_khan_2026'. Token + user stored in localStorage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>TC-LGN-02</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>TS-LGN-02</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>M3 Login</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Empty form blocked by HTML5 required</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Browser anonymous.</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>All fields empty.</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>1. Open /login.html.
-2. Click 'Log in' with empty fields.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Native invalid-input tooltip on Email; no request fired.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>TC-LGN-03</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>TS-LGN-02</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>M3 Login</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Server-side required error</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>API directly hit.</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>POST {} to /api/auth/login</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>1. Send POST /api/auth/login with empty body.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 400 { error: 'email and password are required' }.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>TC-LGN-04</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>TS-LGN-03</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>M3 Login</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Wrong password</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>ali.khan@gmail.com exists.</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>email: ali.khan@gmail.com; password: WrongPass1</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>1. Open /login.html.
-2. Submit with wrong password.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Error banner: 'Invalid email or password' (HTTP 401). User stays on /login.html.</t>
+          <t>Negative, Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Test Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Module Name</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Coverage Type</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>TC-LGN-05</t>
+          <t>TC-LGN-01</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>TS-LGN-03</t>
+          <t>TS-LGN-01</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>M3 Login</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Unknown email</t>
+          <t>User logs in with correct email and password</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -2837,55 +2739,57 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Smoke</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>ghost.user@gmail.com does not exist.</t>
+          <t>An account exists with email ali.khan@gmail.com and password Passw0rd!.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>email: ghost.user@gmail.com; password: AnyPass1</t>
+          <t>Email: ali.khan@gmail.com
+Password: Passw0rd!</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1. Open /login.html.
-2. Submit with unknown email.</t>
+          <t>1. Open the Login page.
+2. Enter the email and password.
+3. Click Log in.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Error banner: 'Invalid email or password'.</t>
+          <t>The user is taken to the home page. The greeting "Hi, ali.khan" appears in the top menu.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>TC-LGN-06</t>
+          <t>TC-LGN-02</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>TS-LGN-03</t>
+          <t>TS-LGN-02</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>M3 Login</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Email lookup is case-sensitive (current behavior)</t>
+          <t>Login form blocks submission when no fields are filled</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2900,50 +2804,50 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Stored email: ali.khan@gmail.com.</t>
+          <t>The user is on the Login page.</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>entered email: ALI.KHAN@gmail.com; password: Passw0rd!</t>
+          <t>Leave Email and Password blank.</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>1. Open /login.html.
-2. Submit with uppercased email.</t>
+          <t>1. Open the Login page.
+2. Click Log in without entering any details.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Login fails: 'Invalid email or password'. Confirms SQL where email = ? exact-match.</t>
+          <t>The form does not submit. The Email field shows a "please fill out this field" prompt.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>TC-LGN-07</t>
+          <t>TC-LGN-03</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>TS-LGN-01</t>
+          <t>TS-LGN-02</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>M3 Login</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Email is trimmed before submit</t>
+          <t>Relevant validation message is shown when required fields are missing</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -2958,51 +2862,50 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>User exists.</t>
+          <t>The user is logging in without filling all required fields.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>email: '  ali.khan@gmail.com  '; password: Passw0rd!</t>
+          <t>Email: blank
+Password: blank</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1. Open /login.html.
-2. Type padded email and password.
-3. Submit.</t>
+          <t>1. Submit a login request with empty email and password.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Login succeeds (whitespace trimmed client-side). Redirected to /.</t>
+          <t>The validation message "email and password are required" is displayed and the user is not logged in.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>TC-LGN-08</t>
+          <t>TC-LGN-04</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>TS-LGN-01</t>
+          <t>TS-LGN-03</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>M3 Login</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Login persists token + user in localStorage</t>
+          <t>Login is rejected when the password is incorrect</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -3017,55 +2920,57 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>User exists.</t>
+          <t>An account exists with email ali.khan@gmail.com.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>email: ali.khan@gmail.com; password: Passw0rd!</t>
+          <t>Email: ali.khan@gmail.com
+Password: WrongPass1</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>1. Log in.
-2. Read localStorage.</t>
+          <t>1. Open the Login page.
+2. Enter the email and a wrong password.
+3. Click Log in.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>token is non-empty JWT. user has id, username, email matching the account.</t>
+          <t>The validation message "Invalid email or password" is displayed. The user remains on the Login page.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>TC-LGN-09</t>
+          <t>TC-LGN-05</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>TS-LGN-04</t>
+          <t>TS-LGN-03</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>M3 Login</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Logged-in user auto-redirected from /login.html</t>
+          <t>Login is rejected when the email is not registered</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -3075,91 +2980,1056 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Token in localStorage.</t>
+          <t>No account exists for ghost.user@gmail.com.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Email: ghost.user@gmail.com
+Password: AnyPass1</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1. Open /login.html directly.</t>
+          <t>1. Open the Login page.
+2. Enter the email and any password.
+3. Click Log in.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Page instantly redirects to /. Login form not rendered.</t>
+          <t>The validation message "Invalid email or password" is displayed.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>TC-LGN-06</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-03</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Login fails when the email casing does not match the registered email</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>The registered email is ali.khan@gmail.com.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Email: ALI.KHAN@gmail.com
+Password: Passw0rd!</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the Login page.
+2. Enter the uppercased email and the correct password.
+3. Click Log in.</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>The validation message "Invalid email or password" is displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-07</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-01</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Email is accepted even with extra spaces around it</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>An account exists for ali.khan@gmail.com.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Email: "  ali.khan@gmail.com  "
+Password: Passw0rd!</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the Login page.
+2. Enter the email with leading and trailing spaces and the correct password.
+3. Click Log in.</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Login succeeds and the user is taken to the home page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-08</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-01</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>User remains logged in after refreshing the page</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>An account exists.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Email: ali.khan@gmail.com
+Password: Passw0rd!</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>1. Log in with the correct details.
+2. Refresh the home page.</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>The user remains logged in. The greeting continues to be shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-09</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-04</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Logged-in user is redirected away from the Login page</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>The user is already logged in.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>No data required.</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>1. While logged in, open the Login page directly.</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>The user is taken straight to the home page. The Login form is not shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>TC-LGN-10</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>TS-LGN-02</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>M3 Login</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>'Sign up' link works from login page</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>"Don't have an account? Sign up" link opens the Sign Up page</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Browser anonymous.</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>1. Open /login.html.
-2. Click 'Sign up'.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>URL becomes /signup.html. 'Create your account' heading visible.</t>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>The user is on the Login page.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>No data required.</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the Login page.
+2. Click the Sign up link.</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>The Sign Up page is displayed with the "Create your account" heading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-11</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-05</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Remember me checkbox is visible on the Login page</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>The user is on the Login page and not logged in.</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>No data required.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the Login page.
+2. Look at the area between the Password field and the Log in button.</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>A checkbox with the label "Remember me" is shown directly above the Log in button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-12</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-05</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Remember me checkbox is unchecked by default on a fresh visit</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>The Login page is opened in a new browser session.</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>No data required.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the Login page in a fresh browser window.
+2. Look at the Remember me checkbox.</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>The Remember me checkbox is unchecked. The user must opt in to a long session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-13</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-05</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Clicking the Remember me label toggles the checkbox</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>The Login page is open.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>No data required.</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the Login page.
+2. Click the area of the "Remember me" label (not the checkbox itself).
+3. Click the same area again.</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Each click toggles the checkbox state. After the first click it becomes checked, after the second it becomes unchecked again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-14</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-07</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Logging in without Remember me ends the session when the tab is closed</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>An account exists with email ali.khan@gmail.com and password Passw0rd!.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Email: ali.khan@gmail.com
+Password: Passw0rd!
+Remember me: unchecked</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the Login page.
+2. Enter the email and password.
+3. Leave Remember me unchecked.
+4. Click Log in.
+5. Close the browser tab.
+6. Open the home page in a new tab.</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>After login the user is on the home page with the greeting visible. After closing and reopening the tab, the home page shows Login and Sign up again. The user is no longer signed in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-15</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-06</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Logging in with Remember me keeps the user signed in across browser restarts</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>An account exists with email sara.n@gmail.com and password Passw0rd!.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Email: sara.n@gmail.com
+Password: Passw0rd!
+Remember me: checked</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the Login page.
+2. Enter the email and password.
+3. Tick Remember me.
+4. Click Log in.
+5. Close the entire browser.
+6. Reopen the browser and open the home page.</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>After login the user is on the home page with the greeting "Hi, sara.n". After closing and reopening the browser, the home page still shows the greeting and the user is still signed in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-16</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-06</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Choosing Remember me on a second login replaces the prior short session cleanly</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>An account exists with email ali.khan@gmail.com and password Passw0rd!.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>First login: Remember me unchecked
+Second login: Remember me checked</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>1. Log in with Remember me unchecked.
+2. Click Logout.
+3. Open the Login page again.
+4. Log in with the same details and Remember me ticked.
+5. Close and reopen the browser.
+6. Open the home page.</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>After step 6 the user is still signed in. There is no leftover short session from the first login interfering with the long session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-17</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-06</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Logout signs the user out from both short and long sessions</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>The user has just logged in with Remember me ticked.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>No data required.</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>1. After logging in with Remember me ticked, click Logout in the top menu.
+2. Open the home page.
+3. Close and reopen the browser, then open the home page again.</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>After step 1 the home page shows Login and Sign up. The greeting and Logout are no longer visible. After step 3 the user is still signed out — the long session does not return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-18</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-07</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>API call without Remember me issues a one-day session</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>An account exists.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Email: ali.khan@gmail.com
+Password: Passw0rd!
+Remember me: false</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>1. Submit a login request with the data above and Remember me set to false.
+2. Inspect the lifetime of the issued session token.</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>The login succeeds and the issued session token is valid for one day from the time of issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-19</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-06</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>API call with Remember me issues a thirty-day session</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>An account exists.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Email: sara.n@gmail.com
+Password: Passw0rd!
+Remember me: true</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>1. Submit a login request with the data above and Remember me set to true.
+2. Inspect the lifetime of the issued session token.</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>The login succeeds and the issued session token is valid for thirty days from the time of issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-20</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-07</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Login request without the Remember me field defaults to a one-day session</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>An account exists. The legacy client does not send a Remember me field.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Email: ali.khan@gmail.com
+Password: Passw0rd! (no Remember me field)</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>1. Submit a login request with email and password only (no Remember me field).
+2. Inspect the lifetime of the issued session token.</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>The login succeeds. The issued session token is valid for one day, the same as if Remember me had been explicitly unchecked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-21</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-06</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Truthy Remember me value other than true is treated as Remember me ON</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>An account exists.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Email: ali.khan@gmail.com
+Password: Passw0rd!
+Remember me: "yes"</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>1. Submit a login request with Remember me set to a truthy non-boolean value such as "yes".
+2. Inspect the lifetime of the issued session token.</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>The login succeeds and the issued session token is valid for thirty days, the same as if Remember me had been explicitly checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>TC-LGN-22</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>TS-LGN-08</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Wrong password with Remember me ticked is still rejected and no session is started</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>An account exists with email ali.khan@gmail.com.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Email: ali.khan@gmail.com
+Password: WrongPass1
+Remember me: checked</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the Login page.
+2. Enter the email and a wrong password.
+3. Tick Remember me.
+4. Click Log in.</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>The validation message "Invalid email or password" is displayed. The user remains on the Login page and is not signed in. No long session is started.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
@@ -3182,17 +4052,17 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="75" customWidth="1" min="10" max="10"/>
-    <col width="75" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>M4 Logout Action</t>
+          <t>M4 Logout</t>
         </is>
       </c>
     </row>
@@ -3238,17 +4108,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>M4 Logout</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Logout clears session and redirects to /</t>
+          <t>User can log out and is returned to the home page</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Verify Logout tears down session from any page.</t>
+          <t>Verify that logout from any page returns the user to the visitor state.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -3265,17 +4135,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>M4 Logout</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Protected pages locked after logout</t>
+          <t>Author-only pages are protected after logout</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Verify /create.html redirect after logout.</t>
+          <t>Verify that protected pages cannot be reached after logout.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -3361,12 +4231,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>M4 Logout</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Logout from homepage</t>
+          <t>User logs out from the home page</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -3386,23 +4256,23 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Logged in.</t>
+          <t>The user is logged in and on the home page.</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1. Open /.
-2. Click 'Logout'.</t>
+          <t>1. Open the home page while logged in.
+2. Click Logout in the top menu.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>URL is /. Nav shows Login + Sign up. localStorage token + user cleared.</t>
+          <t>The user is returned to the home page as a visitor. The top menu now shows Login and Sign up. The greeting and Logout are no longer visible.</t>
         </is>
       </c>
     </row>
@@ -3419,12 +4289,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>M4 Logout</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Logout from /create.html</t>
+          <t>User logs out from the New Post page</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -3444,23 +4314,23 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Logged in.</t>
+          <t>The user is logged in.</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>1. While logged in, open /create.html.
-2. Click 'Logout'.</t>
+          <t>1. Open the New Post page.
+2. Click Logout in the top menu.</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Redirect to /. Nav anonymous. localStorage cleared.</t>
+          <t>The user is returned to the home page as a visitor.</t>
         </is>
       </c>
     </row>
@@ -3477,12 +4347,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>M4 Logout</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Logout from /post.html</t>
+          <t>User logs out from a post detail page</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -3502,23 +4372,23 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Logged in; post id=1 exists.</t>
+          <t>The user is logged in. At least one post exists.</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>/post.html?id=1</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html?id=1.
-2. Click 'Logout'.</t>
+          <t>1. Open any post's detail page.
+2. Click Logout in the top menu.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Redirect to /. Nav anonymous. localStorage cleared.</t>
+          <t>The user is returned to the home page as a visitor.</t>
         </is>
       </c>
     </row>
@@ -3535,12 +4405,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>M4 Logout</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>After logout /create.html redirects to /login.html</t>
+          <t>Visitor is sent to the Login page when trying to write a post after logout</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3560,23 +4430,23 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Just logged out.</t>
+          <t>The user has just logged out.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>1. Logout.
-2. Open /create.html.</t>
+          <t>1. Click Logout from the top menu.
+2. Try to open the New Post page.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Browser navigates to /login.html. 'Log in' heading visible.</t>
+          <t>The Login page opens with the "Log in" heading. The New Post form is not shown.</t>
         </is>
       </c>
     </row>
@@ -3605,11 +4475,11 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="75" customWidth="1" min="10" max="10"/>
-    <col width="75" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3661,17 +4531,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Posts render newest first with full card details</t>
+          <t>Posts are listed newest-first with full card details</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Verify list rendering with title/author/date/preview.</t>
+          <t>Verify the home page renders posts with title, author, date, and a preview.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -3688,17 +4558,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Empty state and fetch-failure handling</t>
+          <t>Empty state and error state are clearly shown</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Verify zero-data and error states.</t>
+          <t>Verify the page when no posts exist or the list cannot be loaded.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -3715,17 +4585,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Content preview truncated at 240 chars</t>
+          <t>Long content is shortened in the list with three dots</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Verify boundary truncation with ellipsis.</t>
+          <t>Verify the 240-character preview boundary.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -3742,17 +4612,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>XSS-safe rendering on listing</t>
+          <t>Special characters in posts are shown safely</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Verify HTML-escape on title/content/author.</t>
+          <t>Verify safe rendering of post content and titles.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -3838,12 +4708,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Posts render with title/author/date/preview</t>
+          <t>Each post shows title, author, date, and a short preview</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -3868,18 +4738,20 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>post: title 'Welcome to MiniBlog'; content 'Hello world'; author ali_khan_2026.</t>
+          <t>Title: Welcome to MiniBlog
+Content: Hello world
+Author: ali.khan</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1. Open /.
-2. Inspect first article.post-card.</t>
+          <t>1. Open the home page.
+2. Look at the first post in the list.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Card shows linked title 'Welcome to MiniBlog', meta 'by ali_khan_2026 · &lt;localized date&gt;', and preview 'Hello world'.</t>
+          <t>The post card shows the title "Welcome to MiniBlog" as a clickable link, the author label "by ali.khan", a date, and the preview text "Hello world".</t>
         </is>
       </c>
     </row>
@@ -3896,12 +4768,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Newest post appears at the top</t>
+          <t>Newest post appears at the top of the list</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3921,22 +4793,23 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Two posts created in known order: P1 then P2.</t>
+          <t>Two posts have been created in known order.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>P1 title: 'First Post'; P2 title: 'Second Post'.</t>
+          <t>First post created: "First Post"
+Second post created: "Second Post"</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>1. Reload /.</t>
+          <t>1. Open the home page after both posts are created.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>P2 'Second Post' appears above P1 'First Post' in the list.</t>
+          <t>"Second Post" appears above "First Post" in the list.</t>
         </is>
       </c>
     </row>
@@ -3953,12 +4826,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Empty state visible when no posts</t>
+          <t>Empty list shows a friendly message</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -3978,22 +4851,22 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Posts table empty.</t>
+          <t>No posts exist on the platform.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1. Reload /.</t>
+          <t>1. Open the home page when there are no posts.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Container shows 'No posts yet. Be the first to write one!'. No post-card elements rendered.</t>
+          <t>The page shows the message "No posts yet. Be the first to write one!" and no post cards are displayed.</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4883,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Content &gt; 240 chars truncated with ellipsis</t>
+          <t>Long content is shortened with three dots in the list</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -4035,22 +4908,23 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Post created with long content.</t>
+          <t>A post with long content exists.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>content = 300 chars (e.g., 300 'a').</t>
+          <t>Content: 300 characters of the letter "a".</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>1. Open / and locate the post.</t>
+          <t>1. Open the home page.
+2. Look at the long post's preview.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Card preview displays the first 240 chars followed by '…'.</t>
+          <t>The preview shows the first 240 characters of the content followed by three dots.</t>
         </is>
       </c>
     </row>
@@ -4067,12 +4941,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Content == 240 chars not truncated</t>
+          <t>Content of exactly 240 characters is shown without three dots</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -4092,22 +4966,23 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Post with exactly 240-char content.</t>
+          <t>A post exists whose content is exactly 240 characters long.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>content = 240 chars 'a'.</t>
+          <t>Content: 240 characters of the letter "a".</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1. Open / and locate the post.</t>
+          <t>1. Open the home page.
+2. Look at the post's preview.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Preview shows full text without '…'.</t>
+          <t>The full content is shown in the preview without trailing dots.</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4999,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Title with HTML-like text rendered as escaped text</t>
+          <t>Title containing HTML-like text is shown as plain text</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -4149,22 +5024,24 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Logged-in author created the post.</t>
+          <t>A post has been created whose title contains script-like text (input-sanitization check).</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>title = '&lt;script&gt;alert(1)&lt;/script&gt;'; content = 'safe body'.</t>
+          <t>Title: &lt;script&gt;alert(1)&lt;/script&gt;
+Content: Sample post content</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>1. Open / and locate the card.</t>
+          <t>1. Open the home page.
+2. Look at the post card with the script-like title.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Card title displays the literal escaped string. No script execution. No &lt;script&gt; tag in DOM.</t>
+          <t>The title is shown as plain readable text. No script runs and no popup appears.</t>
         </is>
       </c>
     </row>
@@ -4181,12 +5058,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Date shown is locale-formatted</t>
+          <t>Post date is shown in a human-readable format</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -4206,22 +5083,23 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Post exists.</t>
+          <t>A post exists.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Any post.</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1. Open / and read the meta line.</t>
+          <t>1. Open the home page.
+2. Look at the date next to the author on a post card.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Date string matches new Date(...).toLocaleString() format (locale-dependent).</t>
+          <t>A human-readable date and time are shown.</t>
         </is>
       </c>
     </row>
@@ -4238,12 +5116,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Click post title opens detail page</t>
+          <t>User opens a post's detail page by clicking its title</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -4263,23 +5141,23 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Post id=1 exists.</t>
+          <t>A post exists.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Title 'Welcome to MiniBlog'.</t>
+          <t>Title: Welcome to MiniBlog</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>1. Open /.
-2. Click the title link of the card.</t>
+          <t>1. Open the home page.
+2. Click the post title "Welcome to MiniBlog".</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>URL becomes /post.html?id=1. Detail H1 matches the card title.</t>
+          <t>The post detail page opens with "Welcome to MiniBlog" as the heading.</t>
         </is>
       </c>
     </row>
@@ -4296,12 +5174,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>M5 Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Failure to fetch shows error block</t>
+          <t>Clear error message appears when posts cannot be loaded</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -4321,23 +5199,22 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Mock /api/posts to return 500 (or stop server).</t>
+          <t>The platform cannot retrieve posts (for example, the service is unavailable).</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Network mock returns HTTP 500.</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1. Open /.
-2. Allow fetch to fail.</t>
+          <t>1. Open the home page when posts cannot be retrieved.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Container shows 'Failed to load posts: &lt;message&gt;'. No post-card elements.</t>
+          <t>A "Failed to load posts" message is shown in place of the list.</t>
         </is>
       </c>
     </row>
@@ -4366,11 +5243,11 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="75" customWidth="1" min="10" max="10"/>
-    <col width="75" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4422,17 +5299,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Render existing post by valid id</t>
+          <t>Existing post is displayed with full details</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Verify happy-path render of title, author, date, content.</t>
+          <t>Verify the happy-path render of a single post.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -4449,17 +5326,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Missing id query parameter</t>
+          <t>Missing post selection is handled gracefully</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Verify 'Missing post id.' message and no API call.</t>
+          <t>Verify that opening the post page without selecting a post is handled.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -4476,17 +5353,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Non-existent or non-numeric id</t>
+          <t>Unknown post selection shows a not-found message</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Verify 'Failed to load post: Post not found' message.</t>
+          <t>Verify that a non-existent post shows a clear error.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -4503,17 +5380,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Author-only Delete button visibility</t>
+          <t>Delete button is shown only to the author of the post</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Verify ownership-driven Delete button rendering.</t>
+          <t>Verify that only the author can see the Delete button.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -4530,17 +5407,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>XSS-safe rendering on detail</t>
+          <t>Special characters in posts are displayed safely</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Verify escaping of title and content.</t>
+          <t>Verify safe rendering of title and content on the detail page.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -4626,12 +5503,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Valid id renders title, author, date, content</t>
+          <t>Existing post displays title, author, date, and full content</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -4651,22 +5528,23 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Post id=1 exists.</t>
+          <t>A post exists on the platform.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>/post.html?id=1</t>
+          <t>An existing post (e.g., title "Welcome to MiniBlog").</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html?id=1.</t>
+          <t>1. Open the home page.
+2. Click the post title to open its detail page.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>H1 = post title. Meta = 'by &lt;author&gt; · &lt;date&gt;'. .post-content shows full content.</t>
+          <t>The page shows the post heading, the author label, the date, and the full content of the post.</t>
         </is>
       </c>
     </row>
@@ -4683,12 +5561,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Missing id shows 'Missing post id.'</t>
+          <t>Post detail page shows a clear message when no post is selected</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -4708,22 +5586,22 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Browser anonymous OK.</t>
+          <t>No post is selected.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>/post.html (no query string)</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html.</t>
+          <t>1. Open the post detail page without selecting a post.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Container shows 'Missing post id.'. No /api/posts/* request made.</t>
+          <t>The page shows the message "Missing post id." and no post is loaded.</t>
         </is>
       </c>
     </row>
@@ -4740,12 +5618,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Non-existent numeric id</t>
+          <t>Opening a non-existent post shows a not-found message</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -4765,22 +5643,22 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Id 999999 does not exist.</t>
+          <t>A post with the chosen reference does not exist.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>/post.html?id=999999</t>
+          <t>Post reference: 999999</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html?id=999999.</t>
+          <t>1. Open the post detail page for the non-existent post.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Container shows 'Failed to load post: Post not found' (HTTP 404).</t>
+          <t>The page shows the message "Failed to load post: Post not found".</t>
         </is>
       </c>
     </row>
@@ -4797,12 +5675,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Non-numeric id</t>
+          <t>Opening a post with an invalid reference shows a not-found message</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -4822,22 +5700,22 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>API returns 404 for non-numeric id.</t>
+          <t>The post reference is not a valid number.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>/post.html?id=abc</t>
+          <t>Post reference: abc</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html?id=abc.</t>
+          <t>1. Open the post detail page using an invalid reference.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Container shows 'Failed to load post: Post not found'.</t>
+          <t>The page shows the message "Failed to load post: Post not found".</t>
         </is>
       </c>
     </row>
@@ -4854,12 +5732,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Author sees Delete button</t>
+          <t>Author sees the Delete button on their own post</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -4879,22 +5757,24 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Logged in as author of post id=1.</t>
+          <t>The user is logged in as the post's author.</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>/post.html?id=1</t>
+          <t>Author: ali.khan
+The author has at least one post.</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html?id=1.</t>
+          <t>1. Log in as Ali Khan.
+2. Open one of Ali Khan's posts.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>#delete-btn visible inside the post card.</t>
+          <t>A Delete button is visible on the post detail page.</t>
         </is>
       </c>
     </row>
@@ -4911,12 +5791,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Anonymous user does NOT see Delete</t>
+          <t>Visitor does not see the Delete button</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -4936,23 +5816,23 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Anonymous.</t>
+          <t>The user is not logged in.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>/post.html?id=1</t>
+          <t>An existing post.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1. Logout.
-2. Open /post.html?id=1.</t>
+          <t>1. Make sure no user is logged in.
+2. Open any post detail page.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>#delete-btn not present in DOM.</t>
+          <t>No Delete button is shown.</t>
         </is>
       </c>
     </row>
@@ -4969,12 +5849,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Non-author logged-in user does NOT see Delete</t>
+          <t>Logged-in user does not see Delete on someone else's post</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -4994,23 +5874,24 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>User B logged in. Post id=1 belongs to User A.</t>
+          <t>User Sara is logged in. The post belongs to Ali Khan.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>User B = sara_n / sara@gmail.com.</t>
+          <t>Other user: sara.n / sara.n@gmail.com
+Post owner: ali.khan</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>1. Log in as User B.
-2. Open /post.html?id=1.</t>
+          <t>1. Log in as Sara.
+2. Open Ali Khan's post detail page.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>#delete-btn not present.</t>
+          <t>No Delete button is shown.</t>
         </is>
       </c>
     </row>
@@ -5027,12 +5908,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Title with HTML escaped on detail</t>
+          <t>Title containing HTML-like text is shown safely</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -5052,22 +5933,23 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Author created post with HTML title.</t>
+          <t>A post has been created whose title contains image/script-like text (input-sanitization check).</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>title = '&lt;img src=x onerror=alert(1)&gt;'.</t>
+          <t>Title: &lt;img src=x onerror=alert(1)&gt;
+Content: Sample content</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1. Open the post's detail page.</t>
+          <t>1. Open that post's detail page.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Title rendered as literal text. No &lt;img&gt; tag in DOM. No alert dialog raised.</t>
+          <t>The title is shown as plain text. No image is loaded and no popup appears.</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5966,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Content preserves whitespace + special chars safely</t>
+          <t>Content with line breaks and special characters is shown safely</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -5109,22 +5991,23 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Post created with mixed content.</t>
+          <t>A post has been created with mixed text content.</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>content = 'Line1\nLine2 &amp; &lt;html&gt;'.</t>
+          <t>Title: Mixed sample
+Content: Line one and line two with &amp; and &lt;html&gt;</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>1. Open the post's detail page.</t>
+          <t>1. Open that post's detail page.</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>.post-content shows the escaped text. No tags rendered.</t>
+          <t>The content is shown as plain readable text. No formatting tags are rendered.</t>
         </is>
       </c>
     </row>
@@ -5141,12 +6024,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>M6 Post Detail</t>
+          <t>Post Detail</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>'← Back to all posts' link returns to /</t>
+          <t>"Back to all posts" link returns the user to the home page</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -5166,23 +6049,23 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Post id=1 exists.</t>
+          <t>A post exists.</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html?id=1.
-2. Click '← Back to all posts'.</t>
+          <t>1. Open any post's detail page.
+2. Click the "Back to all posts" link.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>URL becomes /. Posts list visible.</t>
+          <t>The home page opens with the list of posts.</t>
         </is>
       </c>
     </row>
@@ -5211,17 +6094,17 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="75" customWidth="1" min="10" max="10"/>
-    <col width="75" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>M7 New Post</t>
         </is>
       </c>
     </row>
@@ -5267,17 +6150,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Successful creation with valid title and content</t>
+          <t>Author can publish a post with valid title and content</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Verify create + redirect to detail.</t>
+          <t>Verify the happy-path post creation flow.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -5294,17 +6177,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Required-field validation</t>
+          <t>New Post form enforces required fields</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Verify HTML5 + server required errors.</t>
+          <t>Verify that empty title or content is not accepted.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -5321,17 +6204,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Title boundary (200 char limit)</t>
+          <t>Title length stops at the maximum allowed</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Verify maxlength accept/limit at boundary.</t>
+          <t>Verify the 200-character title boundary.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -5348,17 +6231,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Anonymous user redirected to login</t>
+          <t>Visitor cannot reach the New Post page</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Verify route guard for anonymous access.</t>
+          <t>Verify the access guard for visitors.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -5375,17 +6258,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Token errors clear session and bounce to login</t>
+          <t>Expired session is handled gracefully</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Verify expired/invalid token UX.</t>
+          <t>Verify the session-expired flow during post creation.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -5471,12 +6354,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Publish a valid post</t>
+          <t>Author publishes a new post with valid details</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -5496,24 +6379,25 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Logged in as ali_khan_2026.</t>
+          <t>The user is logged in as ali.khan.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>title: 'QA Roadmap 2026'; content: 'Plans for automation, cross-browser, and security review.'</t>
+          <t>Title: QA Roadmap 2026
+Content: Plans for automation, cross-browser, and security review.</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>1. Click 'New Post' in nav.
-2. Fill title and content.
-3. Click 'Publish'.</t>
+          <t>1. Click New Post in the top menu.
+2. Enter the title and content.
+3. Click Publish.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>URL redirects to /post.html?id=&lt;new id&gt;. H1 matches submitted title. Content matches. Author = ali_khan_2026. Delete button visible.</t>
+          <t>The post detail page opens with the new title as the heading and the full content shown. The author is shown as ali.khan and a Delete button is visible.</t>
         </is>
       </c>
     </row>
@@ -5530,12 +6414,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Empty title blocked by HTML5</t>
+          <t>Title cannot be left empty</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -5555,24 +6439,25 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Logged in.</t>
+          <t>The user is logged in.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>title = ''; content = 'Some content'.</t>
+          <t>Title: blank
+Content: Some content</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1. Open /create.html.
-2. Leave title empty, fill content.
+          <t>1. Open the New Post page.
+2. Leave Title blank, fill Content.
 3. Click Publish.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Native required-field tooltip on title. No request fired.</t>
+          <t>The form does not submit. The Title field shows a "please fill out this field" prompt.</t>
         </is>
       </c>
     </row>
@@ -5589,12 +6474,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Empty content blocked by HTML5</t>
+          <t>Content cannot be left empty</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -5614,24 +6499,25 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Logged in.</t>
+          <t>The user is logged in.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>title = 'Hello'; content = ''.</t>
+          <t>Title: Hello
+Content: blank</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>1. Open /create.html.
-2. Fill title only.
+          <t>1. Open the New Post page.
+2. Fill Title only.
 3. Click Publish.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Native required-field tooltip on content. No request fired.</t>
+          <t>The form does not submit. The Content field shows a "please fill out this field" prompt.</t>
         </is>
       </c>
     </row>
@@ -5648,12 +6534,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Server-side required error</t>
+          <t>Relevant validation message is shown when title or content is missing</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -5673,22 +6559,23 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Valid Bearer token.</t>
+          <t>The user is logged in and submits without filling required fields.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>POST { title: '', content: '' } to /api/posts.</t>
+          <t>Title: blank
+Content: blank</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1. Send POST with empty body and Authorization header.</t>
+          <t>1. Submit a post creation request with title and content empty.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>HTTP 400 { error: 'title and content are required' }.</t>
+          <t>The validation message "title and content are required" is displayed and no post is created.</t>
         </is>
       </c>
     </row>
@@ -5705,12 +6592,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Whitespace-only title rejected</t>
+          <t>Title containing only spaces is treated as empty</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -5730,24 +6617,25 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Logged in.</t>
+          <t>The user is logged in.</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>title = '     '; content = 'valid'.</t>
+          <t>Title: "     "
+Content: valid</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>1. Open /create.html.
-2. Fill title with spaces, content with 'valid'.
-3. Submit.</t>
+          <t>1. Open the New Post page.
+2. Type only spaces in Title and "valid" in Content.
+3. Click Publish.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Client trims to ''. Inline error banner: 'title and content are required'.</t>
+          <t>The validation message "title and content are required" is displayed and no post is created.</t>
         </is>
       </c>
     </row>
@@ -5764,12 +6652,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Title 200 chars accepted (boundary)</t>
+          <t>Title with exactly 200 characters is accepted</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -5789,24 +6677,25 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Logged in.</t>
+          <t>The user is logged in.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>title = 200-char string of 'a'; content = 'Boundary test'.</t>
+          <t>Title: 200 letters of "a"
+Content: Boundary test</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1. Open /create.html.
-2. Paste 200-char title.
-3. Fill content and submit.</t>
+          <t>1. Open the New Post page.
+2. Paste a 200-character title and a short content.
+3. Click Publish.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Post created. Redirect to detail page. Title shows full 200 chars.</t>
+          <t>The post is created. The detail page opens with all 200 characters shown in the heading.</t>
         </is>
       </c>
     </row>
@@ -5823,12 +6712,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Title &gt;200 truncated by HTML5 maxlength</t>
+          <t>Title field stops accepting input after 200 characters</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -5848,23 +6737,23 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Logged in.</t>
+          <t>The user is logged in.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Type 250-char title.</t>
+          <t>Type a 250-character title.</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>1. Open /create.html.
-2. Type 250-char title.</t>
+          <t>1. Open the New Post page.
+2. Type 250 characters into the Title field.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Field accepts only first 200 chars (HTML5 maxlength).</t>
+          <t>The Title field accepts only the first 200 characters.</t>
         </is>
       </c>
     </row>
@@ -5881,12 +6770,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Anonymous user redirected from /create.html</t>
+          <t>Visitor is redirected to Login when opening the New Post page</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -5906,22 +6795,23 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Anonymous.</t>
+          <t>The user is not logged in.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1. Open /create.html with no token.</t>
+          <t>1. Make sure no user is logged in.
+2. Try to open the New Post page.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>URL becomes /login.html immediately. Create form not rendered.</t>
+          <t>The Login page opens. The New Post form is not shown.</t>
         </is>
       </c>
     </row>
@@ -5938,12 +6828,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Missing token gate redirects to login</t>
+          <t>User without a valid session is sent to the Login page when opening New Post</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -5963,22 +6853,23 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Token cleared but user JSON kept.</t>
+          <t>The user's session has been cleared.</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>localStorage.token = removed.</t>
+          <t>No data required.</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>1. Open /create.html.</t>
+          <t>1. Clear the active session.
+2. Open the New Post page.</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Auth.isLoggedIn() = false → redirect to /login.html. No request fires.</t>
+          <t>The Login page opens immediately. The New Post form is not shown.</t>
         </is>
       </c>
     </row>
@@ -5995,12 +6886,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Tampered/expired JWT shows error then redirects</t>
+          <t>Expired session shows an error and returns the user to Login</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -6020,23 +6911,25 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Token manually set to a tampered string in localStorage.</t>
+          <t>The user has an invalid or expired session.</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>title: 'Test'; content: 'Should fail'.</t>
+          <t>Title: Test
+Content: Should fail</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1. Open /create.html (Auth.isLoggedIn() truthy because token exists).
-2. Submit a valid title and content.</t>
+          <t>1. With an invalid session, open the New Post page.
+2. Enter the title and content.
+3. Click Publish.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Error banner contains 'token' (e.g., 'Invalid or expired token'). After ~1.2s user is redirected to /login.html. localStorage token + user are cleared.</t>
+          <t>An error message about an invalid or expired session is shown. After a short delay, the Login page opens. The user must log in again before publishing.</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6946,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>M7 Create Post</t>
+          <t>New Post</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Trims leading/trailing whitespace on title and content</t>
+          <t>Title and content are saved without leading or trailing spaces</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -6078,24 +6971,25 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Logged in.</t>
+          <t>The user is logged in.</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>title: '  Padded Title  '; content: '  body  '.</t>
+          <t>Title: "  Padded Title  "
+Content: "  body  "</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>1. Open /create.html.
-2. Fill padded values.
-3. Submit.</t>
+          <t>1. Open the New Post page.
+2. Enter the padded title and content.
+3. Click Publish.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Stored title is 'Padded Title'. Detail page H1 shows trimmed text.</t>
+          <t>The post detail page shows the heading "Padded Title" without extra spaces and the content trimmed.</t>
         </is>
       </c>
     </row>
@@ -6124,11 +7018,11 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="75" customWidth="1" min="10" max="10"/>
-    <col width="75" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -6180,17 +7074,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Author deletes own post via confirm dialog</t>
+          <t>Author can delete their own post after confirming</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Verify happy-path delete flow.</t>
+          <t>Verify the happy-path delete flow.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -6207,17 +7101,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Cancel confirm dialog leaves post intact</t>
+          <t>Author can cancel the delete confirmation safely</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Verify cancel path triggers no action.</t>
+          <t>Verify that cancelling the prompt keeps the post intact.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -6234,17 +7128,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Non-author API delete blocked</t>
+          <t>Only the post's author can delete the post</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Verify ownership enforcement at API level.</t>
+          <t>Verify ownership is enforced for deletion.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -6261,17 +7155,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Delete non-existent post returns 404</t>
+          <t>Deleting an unknown post shows a not-found message</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Verify 'Post not found' message.</t>
+          <t>Verify the not-found behavior on delete.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -6357,12 +7251,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Author deletes own post and redirects to /</t>
+          <t>Author deletes their own post and is returned to the home page</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -6382,24 +7276,24 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Logged in as author of post id=N.</t>
+          <t>The user is logged in as the post's author.</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>post id=N</t>
+          <t>The author's existing post.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html?id=N.
+          <t>1. Open the post detail page for the author's post.
 2. Click Delete.
-3. Accept the 'Delete this post?' dialog.</t>
+3. Confirm "Delete this post?".</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>URL becomes /. Post no longer in /api/posts. Card no longer in homepage list.</t>
+          <t>The user is returned to the home page. The deleted post no longer appears in the list.</t>
         </is>
       </c>
     </row>
@@ -6416,12 +7310,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Cancel confirm dialog leaves post intact</t>
+          <t>Cancelling the confirmation keeps the post intact</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -6441,24 +7335,24 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Logged in as author of post N.</t>
+          <t>The user is logged in as the post's author.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>post id=N</t>
+          <t>The author's existing post.</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html?id=N.
+          <t>1. Open the post detail page.
 2. Click Delete.
-3. Dismiss the confirm dialog.</t>
+3. Cancel the "Delete this post?" prompt.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>URL unchanged. No DELETE request fired. Post still listed on /.</t>
+          <t>The user remains on the post detail page. The post is not deleted and still appears on the home page.</t>
         </is>
       </c>
     </row>
@@ -6475,12 +7369,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Non-author API delete returns 403</t>
+          <t>A user cannot delete a post that belongs to someone else</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -6500,22 +7394,24 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>User B logged in. Post N belongs to User A.</t>
+          <t>User Sara is logged in. The post belongs to Ali Khan.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>User B token + DELETE /api/posts/N.</t>
+          <t>Other user: sara.n / sara.n@gmail.com
+Post owner: ali.khan</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1. Send DELETE /api/posts/N with User B's Bearer token.</t>
+          <t>1. Log in as Sara.
+2. Try to delete Ali Khan's post.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>HTTP 403 { error: 'You can only delete your own posts' }. Post still exists.</t>
+          <t>The action is rejected with the message "You can only delete your own posts". The post still appears on the home page.</t>
         </is>
       </c>
     </row>
@@ -6532,12 +7428,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Delete non-existent post returns 404</t>
+          <t>Deleting a non-existent post shows a not-found message</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -6557,22 +7453,22 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Valid Bearer token.</t>
+          <t>The user is logged in. The chosen post does not exist.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>DELETE /api/posts/999999.</t>
+          <t>Post reference: 999999</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>1. Send DELETE /api/posts/999999 with token.</t>
+          <t>1. While logged in, try to delete a post that does not exist.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>HTTP 404 { error: 'Post not found' }.</t>
+          <t>The validation message "Post not found" is displayed and no post is deleted.</t>
         </is>
       </c>
     </row>
@@ -6589,12 +7485,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Deleting last remaining post shows empty state</t>
+          <t>Deleting the only existing post shows the empty list message</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -6614,23 +7510,23 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Only one post exists, owned by current user.</t>
+          <t>Only one post exists, owned by the current user.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>post id=N</t>
+          <t>The user's only post.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1. Open /post.html?id=N.
-2. Delete; confirm.</t>
+          <t>1. Open the post detail page.
+2. Click Delete and confirm.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Redirect to /. Homepage shows 'No posts yet. Be the first to write one!'.</t>
+          <t>The home page opens and shows "No posts yet. Be the first to write one!".</t>
         </is>
       </c>
     </row>
@@ -6647,12 +7543,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Missing token blocks delete</t>
+          <t>A delete attempt without a valid session is rejected</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -6672,22 +7568,22 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Post N exists.</t>
+          <t>The user is not signed in.</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>DELETE /api/posts/N with no Authorization header.</t>
+          <t>An existing post.</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>1. Send DELETE without Authorization header.</t>
+          <t>1. Without being signed in, try to delete a post.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>HTTP 401 { error: 'Missing token' }. Post still exists.</t>
+          <t>The action is rejected with the message "Missing token". The post still exists.</t>
         </is>
       </c>
     </row>
@@ -6704,12 +7600,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Tampered token blocks delete</t>
+          <t>A delete attempt with an invalid session is rejected</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -6729,22 +7625,22 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Post N exists.</t>
+          <t>The user's session is invalid or has expired.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Authorization: Bearer abc.def.ghi.</t>
+          <t>An existing post.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1. Send DELETE with tampered Bearer token.</t>
+          <t>1. With an invalid session, try to delete a post.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>HTTP 401 { error: 'Invalid or expired token' }. Post still exists.</t>
+          <t>The action is rejected with the message "Invalid or expired token". The post still exists.</t>
         </is>
       </c>
     </row>
@@ -6761,12 +7657,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>M8 Delete Post</t>
+          <t>Delete Post</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>End-to-end: signup → publish → delete → verify gone</t>
+          <t>End-to-end: register, publish a post, delete it, and verify it is gone</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -6786,25 +7682,30 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Fresh browser, no posts owned by new user.</t>
+          <t>A new visitor with no posts.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>username: noor_e_2026; email: noor.e@gmail.com; password: Strong#22; title: 'Soon to be deleted'; content: 'Bye'.</t>
+          <t>Username: noor.e
+Email: noor.e@gmail.com
+Password: Strong#22
+Title: Soon to be deleted
+Content: Bye</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>1. Sign up new user.
-2. Create post.
-3. Open detail; delete; confirm.
-4. Reload /. 5. Visit /post.html?id=&lt;deleted id&gt;.</t>
+          <t>1. Register a new account.
+2. Create a post with the title and content above.
+3. Open the post's detail page and delete it.
+4. Open the home page.
+5. Try to open the deleted post's detail page again.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>After delete: redirect to /. Post not in homepage list. Detail page shows 'Failed to load post: Post not found'.</t>
+          <t>The post no longer appears on the home page. Opening the deleted post's detail page shows "Failed to load post: Post not found".</t>
         </is>
       </c>
     </row>

--- a/module-wise-test-scenarios-and-cases.xlsx
+++ b/module-wise-test-scenarios-and-cases.xlsx
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -677,10 +677,10 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5234,7 +5234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5426,653 +5426,1627 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Test Cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Scenario ID</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Module Name</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Coverage Type</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-06</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Visitors and members can read comments under a post</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Verify that the comments section, count, and oldest-first list are shown on every post detail page.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Positive, UI, Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-07</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Logged-in members can add a comment; visitors are prompted to log in</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Verify that the comment form appears for signed-in users and is replaced by a login prompt for visitors.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Positive, Negative, UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-08</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Empty or whitespace-only comments are not accepted</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Verify that the comment field is required and that whitespace-only content is rejected by the server.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Negative, Validation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>TS-PDT-09</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Only the comment's author can delete that comment</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Verify that the Delete button on a comment is shown only to its author and that other users cannot remove it.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Validation, Negative, Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Comment length stops at 2000 characters</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Verify the 2000-character comment boundary and that 2001 is rejected.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Boundary, Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-11</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Comments containing HTML-like text are shown safely</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Verify that script-like / image-like text inside a comment is rendered as plain readable text.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Validation, UI, Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Test Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Module Name</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Coverage Type</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>TC-PDT-01</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>TS-PDT-01</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Post Detail</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Existing post displays title, author, date, and full content</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Smoke</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>A post exists on the platform.</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>An existing post (e.g., title "Welcome to MiniBlog").</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>1. Open the home page.
 2. Click the post title to open its detail page.</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>The page shows the post heading, the author label, the date, and the full content of the post.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>TC-PDT-02</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>TS-PDT-02</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Post Detail</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Post detail page shows a clear message when no post is selected</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>No post is selected.</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>No data required.</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>1. Open the post detail page without selecting a post.</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>The page shows the message "Missing post id." and no post is loaded.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>TC-PDT-03</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>TS-PDT-03</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Post Detail</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Opening a non-existent post shows a not-found message</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>A post with the chosen reference does not exist.</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Post reference: 999999</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>1. Open the post detail page for the non-existent post.</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>The page shows the message "Failed to load post: Post not found".</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>TC-PDT-04</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>TS-PDT-03</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Post Detail</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Opening a post with an invalid reference shows a not-found message</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>The post reference is not a valid number.</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Post reference: abc</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>1. Open the post detail page using an invalid reference.</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>The page shows the message "Failed to load post: Post not found".</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>TC-PDT-05</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>TS-PDT-04</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Post Detail</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Author sees the Delete button on their own post</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Smoke</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>The user is logged in as the post's author.</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Author: ali.khan
 The author has at least one post.</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>1. Log in as Ali Khan.
 2. Open one of Ali Khan's posts.</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>A Delete button is visible on the post detail page.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>TC-PDT-06</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>TS-PDT-04</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Post Detail</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Visitor does not see the Delete button</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>The user is not logged in.</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>An existing post.</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>1. Make sure no user is logged in.
 2. Open any post detail page.</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>No Delete button is shown.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>TC-PDT-07</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>TS-PDT-04</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Post Detail</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Logged-in user does not see Delete on someone else's post</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>User Sara is logged in. The post belongs to Ali Khan.</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Other user: sara.n / sara.n@gmail.com
 Post owner: ali.khan</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>1. Log in as Sara.
 2. Open Ali Khan's post detail page.</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>No Delete button is shown.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>TC-PDT-08</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>TS-PDT-05</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Post Detail</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Title containing HTML-like text is shown safely</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>A post has been created whose title contains image/script-like text (input-sanitization check).</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Title: &lt;img src=x onerror=alert(1)&gt;
 Content: Sample content</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>1. Open that post's detail page.</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>The title is shown as plain text. No image is loaded and no popup appears.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>TC-PDT-09</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>TS-PDT-05</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Post Detail</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Content with line breaks and special characters is shown safely</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>A post has been created with mixed text content.</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Title: Mixed sample
 Content: Line one and line two with &amp; and &lt;html&gt;</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>1. Open that post's detail page.</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>The content is shown as plain readable text. No formatting tags are rendered.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>TC-PDT-10</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>TS-PDT-01</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Post Detail</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>"Back to all posts" link returns the user to the home page</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>A post exists.</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>No data required.</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>1. Open any post's detail page.
 2. Click the "Back to all posts" link.</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>The home page opens with the list of posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-11</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-06</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Comments section is visible with empty-state text when a post has no comments</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>A post exists with no comments.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>An existing post.</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the post's detail page.
+2. Scroll to the area below the post.</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>A "Comments (0)" heading is shown. Below it the message "No comments yet. Be the first!" is displayed and no comment cards appear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-12</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-07</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Visitor sees a login prompt instead of the comment form</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>The user is not logged in.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>An existing post.</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>1. Make sure no user is logged in.
+2. Open any post's detail page.
+3. Look at the comments area.</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>A panel reading "Log in to leave a comment." with a Log in link is shown. The comment text box and Post comment button are not displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-13</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-07</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Logged-in user can post a comment that appears immediately under the post</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>The user is logged in. A post exists.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Comment text: "Great post! Thanks for sharing."</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>1. Open a post's detail page while logged in.
+2. Type the comment text into the text box.
+3. Click Post comment.</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>The new comment appears in the list with the user's name and the current date. The counter updates to "Comments (1)". The text box is cleared and ready for another comment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-14</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-08</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Empty comment cannot be submitted from the page</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>The user is logged in.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Leave the comment text box blank.</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>1. Open a post's detail page.
+2. Click Post comment without typing anything.</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>The form does not submit. The text box shows a "please fill out this field" prompt and the comment count does not change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-15</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-08</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Whitespace-only comment is rejected with a clear message</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>The user is logged in.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Comment text: "     " (only spaces and newlines)</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>1. Submit a comment containing only spaces and newlines.</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>The validation message "content is required" is displayed and no comment is added to the post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-16</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-06</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Comments are shown oldest-first and the counter reflects the total</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>A post has three comments added in order: "first", "second", "third".</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Comments: first, second, third</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the post's detail page.
+2. Look at the order of comments and the counter.</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>The counter reads "Comments (3)". The comments appear top to bottom as "first", "second", "third".</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-17</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-09</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Author of a comment can delete it after confirming</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>The user has just posted a comment on a post.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Comment text: "mine to remove"</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>1. On the post's detail page, click Delete on the user's own comment.
+2. Confirm the "Delete this comment?" prompt.</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>The comment is removed from the list. The counter updates to "Comments (0)" and the empty-state message reappears.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-18</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-09</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>User cannot see a Delete button on someone else's comment</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>User Sara is logged in. The comment was written by Ali Khan.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Other user: sara.n / sara.n@gmail.com
+Comment author: ali.khan</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>1. Log in as Sara.
+2. Open the post's detail page.
+3. Look at Ali Khan's comment.</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>The comment is visible with the author's name, but no Delete button is shown on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-19</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-09</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Cross-user delete request is rejected by the platform</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>User Sara has a valid session. The comment belongs to Ali Khan.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Acting user: sara.n
+Comment owner: ali.khan</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>1. While logged in as Sara, attempt to delete one of Ali Khan's comments.</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>The request is rejected with the message "You can only delete your own comments". The comment continues to appear under the post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-20</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-11</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Comment containing HTML-like text is shown as plain text</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>A comment has been added with script-like text (input-sanitization check).</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Comment text: &lt;img src=x onerror=alert(1)&gt; &amp; &lt;script&gt;alert(2)&lt;/script&gt;</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>1. Open the post's detail page.
+2. Look at the comment.</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>The comment is shown as plain readable text. No image is loaded, no script runs, and no popup appears.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-21</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-10</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Comment of exactly 2000 characters is accepted</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>The user is logged in.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Comment text: 2000 letters of "a".</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>1. Submit a comment with 2000 characters of content.</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>The comment is created successfully. The full 2000 characters are saved and shown in the comment list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-22</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-10</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Comment longer than 2000 characters is rejected</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>The user is logged in.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Comment text: 2001 letters of "a".</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>1. Submit a comment with 2001 characters of content.</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>The validation message "comment too long (max 2000 chars)" is displayed and the comment is not saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-23</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-07</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Posting a comment without a valid session is rejected</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>The user is not signed in.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Comment text: "try"</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>1. Without being signed in, attempt to post a comment to an existing post.</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>The action is rejected with the message "Missing token" and no comment is added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>TC-PDT-24</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>TS-PDT-06</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Post Detail</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Posting a comment to a non-existent post returns a clear not-found message</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>The user is logged in. The chosen post does not exist.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Post reference: 999999
+Comment text: "ghost"</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>1. While logged in, attempt to post a comment on the non-existent post.</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>The validation message "Post not found" is displayed and no comment is created.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A11:K11"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A17:K17"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/module-wise-test-scenarios-and-cases.xlsx
+++ b/module-wise-test-scenarios-and-cases.xlsx
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -677,10 +677,10 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -7983,7 +7983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8148,423 +8148,393 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TS-DEL-05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Delete Post</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Delete API actually removes the post from the database</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Verify that a successful delete is reflected in the listing and detail endpoints, not just in the API response.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Regression, Critical, Bug-Guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Test Cases</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Scenario ID</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Module Name</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Coverage Type</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TC-DEL-01</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>TS-DEL-01</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Delete Post</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Author deletes their own post and is returned to the home page</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Smoke</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>The user is logged in as the post's author.</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>The author's existing post.</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>1. Open the post detail page for the author's post.
 2. Click Delete.
 3. Confirm "Delete this post?".</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>The user is returned to the home page. The deleted post no longer appears in the list.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>TC-DEL-02</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>TS-DEL-02</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Delete Post</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Cancelling the confirmation keeps the post intact</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>The user is logged in as the post's author.</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>The author's existing post.</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>1. Open the post detail page.
 2. Click Delete.
 3. Cancel the "Delete this post?" prompt.</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>The user remains on the post detail page. The post is not deleted and still appears on the home page.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TC-DEL-03</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>TS-DEL-03</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Delete Post</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>A user cannot delete a post that belongs to someone else</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>User Sara is logged in. The post belongs to Ali Khan.</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Other user: sara.n / sara.n@gmail.com
 Post owner: ali.khan</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>1. Log in as Sara.
 2. Try to delete Ali Khan's post.</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>The action is rejected with the message "You can only delete your own posts". The post still appears on the home page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>TC-DEL-04</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>TS-DEL-04</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Delete Post</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Deleting a non-existent post shows a not-found message</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Edge</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>The user is logged in. The chosen post does not exist.</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Post reference: 999999</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>1. While logged in, try to delete a post that does not exist.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>The validation message "Post not found" is displayed and no post is deleted.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>TC-DEL-04</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>TS-DEL-04</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Delete Post</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Deleting a non-existent post shows a not-found message</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>The user is logged in. The chosen post does not exist.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Post reference: 999999</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>1. While logged in, try to delete a post that does not exist.</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>The validation message "Post not found" is displayed and no post is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>TC-DEL-05</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>TS-DEL-01</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Delete Post</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Deleting the only existing post shows the empty list message</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Only one post exists, owned by the current user.</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>The user's only post.</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>1. Open the post detail page.
 2. Click Delete and confirm.</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>The home page opens and shows "No posts yet. Be the first to write one!".</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>TC-DEL-06</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>TS-DEL-03</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Delete Post</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>A delete attempt without a valid session is rejected</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>The user is not signed in.</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>An existing post.</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>1. Without being signed in, try to delete a post.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>The action is rejected with the message "Missing token". The post still exists.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>TC-DEL-07</t>
+          <t>TC-DEL-06</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -8579,7 +8549,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>A delete attempt with an invalid session is rejected</t>
+          <t>A delete attempt without a valid session is rejected</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -8599,7 +8569,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>The user's session is invalid or has expired.</t>
+          <t>The user is not signed in.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -8609,57 +8579,114 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1. With an invalid session, try to delete a post.</t>
+          <t>1. Without being signed in, try to delete a post.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>The action is rejected with the message "Invalid or expired token". The post still exists.</t>
+          <t>The action is rejected with the message "Missing token". The post still exists.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>TC-DEL-07</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>TS-DEL-03</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Delete Post</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>A delete attempt with an invalid session is rejected</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>The user's session is invalid or has expired.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>An existing post.</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>1. With an invalid session, try to delete a post.</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>The action is rejected with the message "Invalid or expired token". The post still exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>TC-DEL-08</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>TS-DEL-01</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Delete Post</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>End-to-end: register, publish a post, delete it, and verify it is gone</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Smoke</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>A new visitor with no posts.</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Username: noor.e
 Email: noor.e@gmail.com
@@ -8668,7 +8695,7 @@
 Content: Bye</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>1. Register a new account.
 2. Create a post with the title and content above.
@@ -8677,15 +8704,189 @@
 5. Try to open the deleted post's detail page again.</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>The post no longer appears on the home page. Opening the deleted post's detail page shows "Failed to load post: Post not found".</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>TC-DEL-09</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>TS-DEL-05</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Delete Post</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>After a successful delete, the post no longer appears in the public list</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>The user is logged in as the post's author and the post exists.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Title: Delete me — bug-guard
+Content: Should be gone after delete.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>1. While logged in, send the delete request for the user's post.
+2. Confirm the request returns a successful response.
+3. Refresh the home page (or fetch the public posts list).</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>The deleted post is not present in the public posts list. The deleted post's detail page shows "Post not found". Notes: this case guards against the regression where the delete API returns OK but the row is never removed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>TC-DEL-10</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>TS-DEL-05</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Delete Post</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>After a successful delete, opening the post directly shows a not-found message</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>The user has just deleted their own post.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>The deleted post's reference.</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>1. After deleting a post, open its detail page directly using its reference.</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>The page shows "Failed to load post: Post not found". The post can no longer be retrieved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TC-DEL-11</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>TS-DEL-05</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Delete Post</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Re-deleting the same post a second time is rejected as not found</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>The user has already deleted a post.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>The previously-deleted post's reference.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>1. Send a second delete request for the same post the user just deleted.</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>The second attempt is rejected with the message "Post not found". Notes: protects against the bug where the row was never actually removed, in which case a second delete would still report success.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A11:K11"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
